--- a/VerveStacks_BRA_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23FD2846-116E-47EC-BD41-390D96721D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C15EB0B-3C9B-468D-A57B-9CE4878B0141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4253,7 +4253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99DC4DA9-FF04-4049-A735-A08FC7018FE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1087A969-7526-4A0E-BD8D-4E30D139B60E}">
   <dimension ref="B2:AF532"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14436,7 +14436,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E057A2F-69EC-4E76-947A-B4FC278B7292}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8720AFE-8E80-481B-B0C2-DA61FAA236B1}">
   <dimension ref="B9:L42"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26782,7 +26782,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F09F6F-B143-4DD7-BEA1-60BD4139D54A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F65E821B-9888-4EDD-A66F-EDE605C1E8E7}">
   <dimension ref="A1:I219"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C15EB0B-3C9B-468D-A57B-9CE4878B0141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4C9245A-69C4-44AD-AA4F-FF5FD546DD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4253,7 +4253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1087A969-7526-4A0E-BD8D-4E30D139B60E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B3C81E-57BA-419E-9A9B-4A2EBC835498}">
   <dimension ref="B2:AF532"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14436,7 +14436,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8720AFE-8E80-481B-B0C2-DA61FAA236B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C85F813-8302-44A2-AB67-FC326E639267}">
   <dimension ref="B9:L42"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26782,7 +26782,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F65E821B-9888-4EDD-A66F-EDE605C1E8E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC4D0F6-E381-480B-A9FE-F08DDC97A7F2}">
   <dimension ref="A1:I219"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
